--- a/assessment_forms/017_lysosome_biology_quiz--assessment_forms.xlsx
+++ b/assessment_forms/017_lysosome_biology_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lysosome-biology-quiz</t>
+          <t>Lysosome Basics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lysosome-biology</t>
+          <t>Lysosome Structure</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lysosome-definition</t>
+          <t>Lysosome Function</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lysosome-functions</t>
+          <t>Lysosome Interactions</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lysosome-structure</t>
+          <t>Autophagy</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lysosome-biology-quiz-time</t>
+          <t>Lysosome Regulation</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lysosome-biology-quiz-date</t>
+          <t>Lysosome Dysfunction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lysosome-biology-quiz-email</t>
+          <t>Lysosome Membrane</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lysosome-biology-quiz-phone</t>
+          <t>Lysosome Enzymes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lysosome-biology-quiz-note</t>
+          <t>Lysosome and Other Organelles</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lysosome-biology-quiz-select-one</t>
+          <t>Lysosome pH</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,264 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lysosome-biology-quiz-select-multiple</t>
+          <t>Lysosome Questions</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-multiple</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-multiple</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-multiple</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-one</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-one</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-one</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-one</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-one</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-one</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-one</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>lysosome-biology-quiz-select-one</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1052,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1080,510 +827,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[{'option-label':_'option-1'},_{'option-value':_'value-1'}]</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'option-label': 'option-1'}, {'option-value': 'value-1'}]</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[{'option-label':_'option-2'},_{'option-value':_'value-2'}]</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[{'option-label': 'option-2'}, {'option-value': 'value-2'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>page_11_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-3'},_{'option-value':_'value-3'}]</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-3'}, {'option-value': 'value-3'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>page_12_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-4'},_{'option-value':_'value-4'}]</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-4'}, {'option-value': 'value-4'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>page_12_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-5'},_{'option-value':_'value-5'}]</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-5'}, {'option-value': 'value-5'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>page_12_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-6'},_{'option-value':_'value-6'}]</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-6'}, {'option-value': 'value-6'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>page_13_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-7'},_{'option-value':_'value-7'}]</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-7'}, {'option-value': 'value-7'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>page_13_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-8'},_{'option-value':_'value-8'}]</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-8'}, {'option-value': 'value-8'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>page_14_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-9'},_{'option-value':_'value-9'}]</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-9'}, {'option-value': 'value-9'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>page_14_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-10'},_{'option-value':_'value-10'}]</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-10'}, {'option-value': 'value-10'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>page_15_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-11'},_{'option-value':_'value-11'}]</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-11'}, {'option-value': 'value-11'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>page_15_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>page_16_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-12'},_{'option-value':_'value-12'}]</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-12'}, {'option-value': 'value-12'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>page_16_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-13'},_{'option-value':_'value-13'}]</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-13'}, {'option-value': 'value-13'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>page_16_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-14'},_{'option-value':_'value-14'}]</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-14'}, {'option-value': 'value-14'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-15'},_{'option-value':_'value-15'}]</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-15'}, {'option-value': 'value-15'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-16'},_{'option-value':_'value-16'}]</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-16'}, {'option-value': 'value-16'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-17'},_{'option-value':_'value-17'}]</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-17'}, {'option-value': 'value-17'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>page_18_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-18'},_{'option-value':_'value-18'}]</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-18'}, {'option-value': 'value-18'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>page_18_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-19'},_{'option-value':_'value-19'}]</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-19'}, {'option-value': 'value-19'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>page_19_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-20'},_{'option-value':_'value-20'}]</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-20'}, {'option-value': 'value-20'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>page_19_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-21'},_{'option-value':_'value-21'}]</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-21'}, {'option-value': 'value-21'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-22'},_{'option-value':_'value-22'}]</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-22'}, {'option-value': 'value-22'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-23'},_{'option-value':_'value-23'}]</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-23'}, {'option-value': 'value-23'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-24'},_{'option-value':_'value-24'}]</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-24'}, {'option-value': 'value-24'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>page_23_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>[{'option-label':_'option-25'},_{'option-value':_'value-25'}]</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[{'option-label': 'option-25'}, {'option-value': 'value-25'}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>page_23_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
